--- a/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-28T15:23:31+00:00</t>
+    <t>2025-09-16T15:19:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-16T15:19:32+00:00</t>
+    <t>2025-09-17T15:34:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-17T15:34:10+00:00</t>
+    <t>2025-09-18T15:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-18T15:44:05+00:00</t>
+    <t>2025-09-23T09:34:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-23T09:34:38+00:00</t>
+    <t>2025-09-23T15:19:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-23T15:19:35+00:00</t>
+    <t>2025-09-23T16:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-23T16:34:28+00:00</t>
+    <t>2025-09-24T07:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-24T07:45:14+00:00</t>
+    <t>2025-09-24T09:52:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-24T09:52:59+00:00</t>
+    <t>2025-09-24T12:03:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-24T12:03:32+00:00</t>
+    <t>2025-09-24T15:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-vs-edqm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-24T15:30:16+00:00</t>
+    <t>2025-09-29T08:50:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
